--- a/Result/profitability/9921.xlsx
+++ b/Result/profitability/9921.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.22</v>
       </c>
       <c r="M2" t="n">
-        <v>0.18875</v>
+        <v>0.2325</v>
       </c>
       <c r="N2" t="n">
-        <v>18.8575</v>
+        <v>19.57875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.39</v>
       </c>
       <c r="M3" t="n">
-        <v>0.32875</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>19.375</v>
+        <v>20.7225</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -795,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.98</v>
       </c>
       <c r="M4" t="n">
-        <v>0.99</v>
+        <v>1.075</v>
       </c>
       <c r="N4" t="n">
-        <v>20.71125</v>
+        <v>21.5175</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -914,13 +914,13 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.2525</v>
       </c>
       <c r="N5" t="n">
-        <v>21.25125</v>
+        <v>21.72625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.63</v>
       </c>
       <c r="M6" t="n">
-        <v>1.25375</v>
+        <v>1.345</v>
       </c>
       <c r="N6" t="n">
-        <v>21.38625</v>
+        <v>21.73375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>2.58</v>
       </c>
       <c r="M7" t="n">
-        <v>1.465</v>
+        <v>1.72625</v>
       </c>
       <c r="N7" t="n">
-        <v>22.1025</v>
+        <v>22.6675</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,13 +1391,13 @@
         <v>1.58</v>
       </c>
       <c r="M8" t="n">
-        <v>1.72125</v>
+        <v>1.9875</v>
       </c>
       <c r="N8" t="n">
-        <v>22.64</v>
+        <v>23.21625</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,13 +1409,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9921</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>16665</v>
+      </c>
+      <c r="D75" t="n">
+        <v>12625</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4040</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>996</v>
+      </c>
+      <c r="K75" t="n">
+        <v>635</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.23875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.40125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-4.176470588235294</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.609999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2348446255731025</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.799999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1859099804305282</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
